--- a/05_synthesis/governance_gap_taxonomy.xlsx
+++ b/05_synthesis/governance_gap_taxonomy.xlsx
@@ -1,13 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Gap Taxonomy" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gap_Taxonomy" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code_to_theme_v1" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -27,21 +28,14 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="001F4E78"/>
-        <bgColor rgb="001F4E78"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -56,10 +50,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -426,165 +423,700 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="55" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="51.3" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="24.3" customWidth="1" min="5" max="5"/>
+    <col width="27" customWidth="1" min="6" max="6"/>
+    <col width="27" customWidth="1" min="7" max="7"/>
+    <col width="52.2" customWidth="1" min="8" max="8"/>
+    <col width="70" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>gap_id</t>
         </is>
       </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>gap_instance</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>dimensions</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>evidence_refs_etecom_tableV</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evidence_study_ids</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>candidate_evidence_cells</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>confidence</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>I. Architecture Agnosticism (AAG)</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>AAG-1</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Limited multi-cloud governance contextualisation</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>[2],[4],[12],[13]</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>NRM-01, STU-02, NRM-02, NRM-03</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>EV-009, EV-008, EV-011, EV-005</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>candidate_evidence_cells = coded cells of the cited sources in the gap dimensions (derived link); no segment-level justification per gap instance was recorded in v1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>I. Architecture Agnosticism (AAG)</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>AAG-2</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Provider heterogeneity governance gap</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>[3],[5],[6]</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>STU-01, STU-03, STU-08</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>EV-014, EV-007, EV-002</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>candidate_evidence_cells = coded cells of the cited sources in the gap dimensions (derived link); no segment-level justification per gap instance was recorded in v1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>II. Cross-Provider Policy Coordination (CPCG)</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>CPCG-1</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Cross-provider policy synchronisation</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>D1, D3</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>[3],[5]</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>STU-01, STU-03</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>EV-014, EV-042, EV-007, EV-035</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>candidate_evidence_cells = coded cells of the cited sources in the gap dimensions (derived link); no segment-level justification per gap instance was recorded in v1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>II. Cross-Provider Policy Coordination (CPCG)</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>CPCG-2</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Provider-specific control translation</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>D1, D3</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr"/>
+      <c r="F5" s="2" t="inlineStr"/>
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>moderate-confidence inference (cross-framework comparison)</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>candidate_evidence_cells = coded cells of the cited sources in the gap dimensions (derived link); no segment-level justification per gap instance was recorded in v1. The v1 workbook (Frequency &amp; Themes) attributes CPCG-2 to Diningrat p.70006 and Ali p.11, but published Table V marks it as having no direct literature evidence - reconcile in the journal version.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>III. Shared-Responsibility Boundary (SRBG)</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>SRBG-1</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Cross-provider accountability reconciliation</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>D4</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>[3],[6],[13]</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>STU-01, STU-08, NRM-03</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>EV-056, EV-044, EV-047</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>candidate_evidence_cells = coded cells of the cited sources in the gap dimensions (derived link); no segment-level justification per gap instance was recorded in v1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>III. Shared-Responsibility Boundary (SRBG)</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>SRBG-2</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Accountability boundary ambiguity</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>D4</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>[3],[6]</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>STU-01, STU-08</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>EV-056, EV-044</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>candidate_evidence_cells = coded cells of the cited sources in the gap dimensions (derived link); no segment-level justification per gap instance was recorded in v1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>IV. Cross-Cloud Risk-Posture Normalisation (CRPNG)</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>CRPNG-1</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Monitoring-data normalisation</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>D1, D5</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>[3],[5]</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>STU-01, STU-03</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>EV-014, EV-070, EV-007, EV-063</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>candidate_evidence_cells = coded cells of the cited sources in the gap dimensions (derived link); no segment-level justification per gap instance was recorded in v1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>IV. Cross-Cloud Risk-Posture Normalisation (CRPNG)</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>CRPNG-2</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Guidance-obligation distinction</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>D1, D5</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr"/>
+      <c r="F9" s="2" t="inlineStr"/>
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>moderate-confidence inference (advisory status of CSA v5)</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>candidate_evidence_cells = coded cells of the cited sources in the gap dimensions (derived link); no segment-level justification per gap instance was recorded in v1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>V. Federated IAM Governance (FIAMG)</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>FIAMG-1</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Cross-provider trust-relationship governance</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>D6</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>[7],[10],[13]</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>STU-05, STU-10, NRM-03</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>EV-076, EV-083, EV-075</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>candidate_evidence_cells = coded cells of the cited sources in the gap dimensions (derived link); no segment-level justification per gap instance was recorded in v1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>V. Federated IAM Governance (FIAMG)</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>FIAMG-2</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Lifecycle synchronisation governance</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>D6</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>[7],[13]</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>STU-05, NRM-03</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>EV-076, EV-075</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>candidate_evidence_cells = coded cells of the cited sources in the gap dimensions (derived link); no segment-level justification per gap instance was recorded in v1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>V. Federated IAM Governance (FIAMG)</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>FIAMG-3</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Token validation and protocol interoperability governance</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>D6</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>[7],[13]</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>STU-05, NRM-03</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>EV-076, EV-075</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>candidate_evidence_cells = coded cells of the cited sources in the gap dimensions (derived link); no segment-level justification per gap instance was recorded in v1.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="41.4" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="70" customWidth="1" min="3" max="3"/>
+    <col width="70" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>theme</t>
+        </is>
+      </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>gap_category</t>
+          <t>dimension</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>gap_description</t>
+          <t>code_pattern_constituting_gap</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>supporting_evidence_ids</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>supporting_study_ids</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>severity</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>notes</t>
+          <t>rationale_v1</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>GAP-01</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Identity &amp; Access Management</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>EXAMPLE: No standardized cross-provider identity federation approach.</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>EV-0001</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>STU-0001</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>TEMPLATE (High/Medium/Low)</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>EXAMPLE row - replace with real gap taxonomy entry</t>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>AAG - Architecture Agnosticism</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>D1.1 dominates the frameworks (all three code D1.1/D1.3, never D1.4); operational multi-cloud (D1.4) confined to two empirical studies.</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">if a framework doesn't know multi-cloud exists (D1), then its governance (D2), enforcement (D3), everything else is automatically blind to it too. </t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>GAP-02</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Monitoring &amp; Audit</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>EXAMPLE: Lack of unified, vendor-neutral audit trail format across clouds.</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>EV-0002</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>STU-0001</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>TEMPLATE (High/Medium/Low)</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>EXAMPLE row - replace with real gap taxonomy entry</t>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>CPCG - Cross-Provider Policy Coordination</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>D3.4 (policy specification only) recurs corpus-wide; D3.1 preventive controls appear only inside single providers - no D3.1 at cross-provider level.</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">D3.4 seven times — your most frequent thin code. The three Yes ratings (ISO, NIST, Hu) all sit in single-provider or architecture-agnostic context. Convergence → gap → CPCG-1, "no policy synchronisation across providers." 
+while reading the D3 evidence, two segments describe a different, second absence: Diningrat (p. 70006) and Ali (p. 11) both describe meaning changing when one policy is translated into AWS SCPs vs Azure Policies vs GCP bindings. That is not "no synchronisation" — that is semantic drift, a structurally separate problem → it earns its own row, CPCG-2, with exactly those two sources in the Evidence column. </t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>GAP-03</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Policy &amp; Compliance</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>EXAMPLE: No vendor-neutral compliance reporting standard.</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>EV-0004</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>STU-0002</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>TEMPLATE (High/Medium/Low)</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>EXAMPLE row - replace with real gap taxonomy entry</t>
-        </is>
-      </c>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>SRBG - Shared Responsibility Boundary</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>D4</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>D4.4 (referenced, not allocated) dominates the literature; D4.3 allocations exist only inside single-provider framework models - never reconciled across providers.</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>CRPNG - Cross-Cloud Risk Posture Normalisation</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>D5</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>D5.DE monitoring exists per provider; no code instance normalises posture across providers - D5.X and per-provider D5.DE constitute the gap.</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>FIAMG - Federated IAM Governance</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>D6</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>D6.IF exists (CSA, Poehn, Kaur, Cuzzocrea) but as guidance/technique; D6.AA without D6.IF in the frameworks; multiple n/a - no framework mandates cross-provider IdP governance.</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
